--- a/Data/Home/Context.UltravioletLevel.xlsx
+++ b/Data/Home/Context.UltravioletLevel.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H225"/>
+  <dimension ref="A1:I217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709234852</v>
+        <v>1711840694</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709251668</v>
+        <v>1711851897</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709259065</v>
+        <v>1711860719</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709267499</v>
+        <v>1711872616</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -593,10 +601,11 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709272736</v>
+        <v>1711880618</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -625,10 +634,11 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709280212</v>
+        <v>1711882232</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -657,10 +667,11 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709281540</v>
+        <v>1711913559</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +704,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709282123</v>
+        <v>1711929413</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -721,10 +733,11 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +756,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709232438</v>
+        <v>1711938091</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -753,10 +766,11 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +789,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709245128</v>
+        <v>1711948715</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -785,10 +799,11 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +822,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709251586</v>
+        <v>1711954847</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +836,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +855,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709259361</v>
+        <v>1711964957</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -849,10 +865,11 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +888,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709263182</v>
+        <v>1711967181</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -881,10 +898,11 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +921,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709269429</v>
+        <v>1711968330</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -913,10 +931,11 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +954,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709271370</v>
+        <v>1711999357</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +968,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +987,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709272010</v>
+        <v>1712015668</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -977,10 +997,11 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1020,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709328530</v>
+        <v>1712024666</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1009,10 +1030,11 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1053,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709336942</v>
+        <v>1712035118</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1041,10 +1063,11 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1086,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709343874</v>
+        <v>1712041462</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1100,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1119,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709352560</v>
+        <v>1712051242</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1133,7 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1152,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709359027</v>
+        <v>1712053176</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1166,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1185,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709360067</v>
+        <v>1712054031</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1199,7 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1218,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709414303</v>
+        <v>1712085332</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1232,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1251,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709422516</v>
+        <v>1712101749</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1265,7 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1284,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709429241</v>
+        <v>1712110832</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1298,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1317,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709438073</v>
+        <v>1712121146</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1297,10 +1327,11 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1350,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709444578</v>
+        <v>1712126314</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1329,10 +1360,11 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1383,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709445780</v>
+        <v>1712135275</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1361,10 +1393,11 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1416,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709490514</v>
+        <v>1712137127</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1430,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1449,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709502974</v>
+        <v>1712137969</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1425,10 +1459,11 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1482,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709509259</v>
+        <v>1712171005</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1457,10 +1492,11 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1515,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709518200</v>
+        <v>1712187770</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1489,10 +1525,11 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1548,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709523634</v>
+        <v>1712196428</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1562,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1581,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709532397</v>
+        <v>1712206959</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1553,10 +1591,11 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1614,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709535068</v>
+        <v>1712212344</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1585,10 +1624,11 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1647,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709535924</v>
+        <v>1712221980</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1617,10 +1657,11 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1680,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709576496</v>
+        <v>1712223839</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1694,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1713,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709589581</v>
+        <v>1712224655</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1681,10 +1723,11 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1746,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709596805</v>
+        <v>1712258405</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1713,10 +1756,11 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1779,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709605669</v>
+        <v>1712274889</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1745,10 +1789,11 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1812,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709611224</v>
+        <v>1712283250</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1826,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1845,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709619295</v>
+        <v>1712294355</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1809,10 +1855,11 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1878,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709621675</v>
+        <v>1712300185</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1841,10 +1888,11 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1911,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709622380</v>
+        <v>1712310057</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1873,10 +1921,11 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1944,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709663644</v>
+        <v>1712312299</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1909,6 +1958,7 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +1977,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709677089</v>
+        <v>1712313280</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1937,10 +1987,11 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2010,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709684257</v>
+        <v>1712358223</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1969,10 +2020,11 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2043,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709693091</v>
+        <v>1712368808</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2001,10 +2053,11 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2076,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709697493</v>
+        <v>1712377527</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2090,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2109,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709705314</v>
+        <v>1712388982</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2123,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2142,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709706688</v>
+        <v>1712396446</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2101,6 +2156,7 @@
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2175,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709707326</v>
+        <v>1712397837</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2189,7 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2208,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709749995</v>
+        <v>1712431415</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2222,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2241,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709763285</v>
+        <v>1712447869</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2255,7 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2274,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709769866</v>
+        <v>1712456427</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2288,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2307,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709777144</v>
+        <v>1712467766</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2321,7 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2340,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709781180</v>
+        <v>1712473231</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2354,7 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2373,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709788284</v>
+        <v>1712483136</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2325,6 +2387,7 @@
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2406,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709789737</v>
+        <v>1712485153</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2420,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2439,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709790265</v>
+        <v>1712486197</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,6 +2453,7 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2472,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709836517</v>
+        <v>1712530250</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2486,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2505,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709849601</v>
+        <v>1712540717</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2453,6 +2519,7 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2538,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1709855789</v>
+        <v>1712549367</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2552,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2571,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1709863508</v>
+        <v>1712560377</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2513,10 +2581,11 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2604,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1709867322</v>
+        <v>1712567808</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2545,10 +2614,11 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2637,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1709873971</v>
+        <v>1712569155</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2577,10 +2647,11 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2670,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1709875497</v>
+        <v>1712603476</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2684,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2703,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1709876149</v>
+        <v>1712619774</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2641,10 +2713,11 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2736,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1709924637</v>
+        <v>1712628899</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2673,10 +2746,11 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2769,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1709938081</v>
+        <v>1712639792</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2705,10 +2779,11 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2802,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1709944780</v>
+        <v>1712646339</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2816,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2835,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1709953431</v>
+        <v>1712656363</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2769,10 +2845,11 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2868,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1709957374</v>
+        <v>1712658105</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2801,10 +2878,11 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2901,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1709965200</v>
+        <v>1712659035</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2833,10 +2911,11 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +2934,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1709967554</v>
+        <v>1712689942</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +2948,7 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +2967,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1709968398</v>
+        <v>1712706470</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2897,10 +2977,11 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3000,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1710009217</v>
+        <v>1712715234</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2929,10 +3010,11 @@
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3033,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1710022355</v>
+        <v>1712726271</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2961,10 +3043,11 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3066,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1710028990</v>
+        <v>1712732265</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2997,6 +3080,7 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3099,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710036773</v>
+        <v>1712742187</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3025,10 +3109,11 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3132,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710041093</v>
+        <v>1712744246</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3057,10 +3142,11 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3165,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710048970</v>
+        <v>1712745042</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3089,10 +3175,11 @@
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3198,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710050844</v>
+        <v>1712776701</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3125,6 +3212,7 @@
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3231,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710051606</v>
+        <v>1712793250</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3153,10 +3241,11 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3264,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710096311</v>
+        <v>1712801452</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3185,10 +3274,11 @@
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3297,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710108713</v>
+        <v>1712811406</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3217,10 +3307,11 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3330,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710115451</v>
+        <v>1712817518</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3344,7 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3363,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710123554</v>
+        <v>1712827128</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3281,10 +3373,11 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3396,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710128113</v>
+        <v>1712829382</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3313,10 +3406,11 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3429,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710136362</v>
+        <v>1712830455</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3345,10 +3439,11 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3462,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710137856</v>
+        <v>1712863081</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3381,6 +3476,7 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3495,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710138608</v>
+        <v>1712878860</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3409,10 +3505,11 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3528,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710195375</v>
+        <v>1712887351</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3441,10 +3538,11 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3561,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710205372</v>
+        <v>1712897460</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3473,10 +3571,11 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3594,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710212924</v>
+        <v>1712903862</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3608,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3627,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710222605</v>
+        <v>1712914014</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3541,6 +3641,7 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3660,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710229098</v>
+        <v>1712916716</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3674,7 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3693,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710230524</v>
+        <v>1712917754</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3707,7 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3726,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710269654</v>
+        <v>1712962081</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3740,7 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3759,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710284482</v>
+        <v>1712972949</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3669,6 +3773,7 @@
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3792,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710292401</v>
+        <v>1712981611</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3701,6 +3806,7 @@
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3825,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710301626</v>
+        <v>1712993240</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3729,10 +3835,11 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3858,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710307600</v>
+        <v>1713000804</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3761,10 +3868,11 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3891,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710316157</v>
+        <v>1713002224</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3793,10 +3901,11 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +3924,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710318705</v>
+        <v>1713035468</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3829,6 +3938,7 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +3957,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710319313</v>
+        <v>1713052237</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3857,10 +3967,11 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +3990,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710353929</v>
+        <v>1713060425</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3889,10 +4000,11 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4023,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710367897</v>
+        <v>1713069923</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3921,10 +4033,11 @@
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4056,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710375343</v>
+        <v>1713075936</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4070,7 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4089,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710384192</v>
+        <v>1713086319</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3985,10 +4099,11 @@
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4122,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710388329</v>
+        <v>1713089123</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4017,10 +4132,11 @@
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4155,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710395588</v>
+        <v>1713090137</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4049,10 +4165,11 @@
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4188,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710398080</v>
+        <v>1713134217</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4085,6 +4202,7 @@
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4221,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1710398957</v>
+        <v>1713145128</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4113,10 +4231,11 @@
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4254,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1710443687</v>
+        <v>1713154092</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4145,10 +4264,11 @@
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4287,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1710458083</v>
+        <v>1713165387</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4181,6 +4301,7 @@
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4320,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1710465022</v>
+        <v>1713172242</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4209,10 +4330,11 @@
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4353,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1710473074</v>
+        <v>1713173791</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4241,10 +4363,11 @@
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4386,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1710478017</v>
+        <v>1713209045</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4273,10 +4396,11 @@
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4419,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1710485132</v>
+        <v>1713226064</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4433,7 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4452,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1710486358</v>
+        <v>1713235104</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4337,10 +4462,11 @@
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4485,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1710486899</v>
+        <v>1713245347</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4369,10 +4495,11 @@
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4518,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1710537770</v>
+        <v>1713251853</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4401,10 +4528,11 @@
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4551,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1710545495</v>
+        <v>1713261886</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4437,6 +4565,7 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4584,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1710552083</v>
+        <v>1713264932</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4465,10 +4594,11 @@
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4617,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1710559847</v>
+        <v>1713265930</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4497,10 +4627,11 @@
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4650,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1710565192</v>
+        <v>1713295183</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4533,6 +4664,7 @@
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4683,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1710566245</v>
+        <v>1713311908</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4561,10 +4693,11 @@
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4716,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1710615308</v>
+        <v>1713320945</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4593,10 +4726,11 @@
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4749,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1710627873</v>
+        <v>1713331396</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4625,10 +4759,11 @@
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4782,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1710633864</v>
+        <v>1713337450</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4661,6 +4796,7 @@
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4815,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1710641926</v>
+        <v>1713346630</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4689,10 +4825,11 @@
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4848,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1710646192</v>
+        <v>1713348463</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4721,10 +4858,11 @@
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +4881,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1710653982</v>
+        <v>1713349302</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4753,10 +4891,11 @@
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +4914,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1710655866</v>
+        <v>1713393451</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4789,6 +4928,7 @@
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +4947,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1710656645</v>
+        <v>1713404557</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4817,10 +4957,11 @@
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +4980,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1710701378</v>
+        <v>1713413306</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4849,10 +4990,11 @@
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5013,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1710715186</v>
+        <v>1713424555</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4885,6 +5027,7 @@
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5046,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1710722828</v>
+        <v>1713432094</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4913,10 +5056,11 @@
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5079,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1710731690</v>
+        <v>1713433466</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4945,10 +5089,11 @@
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5112,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1710736969</v>
+        <v>1713468679</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4977,10 +5122,11 @@
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5145,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1710745035</v>
+        <v>1713484922</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5013,6 +5159,7 @@
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5178,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1710746482</v>
+        <v>1713492877</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5041,10 +5188,11 @@
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5211,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1710747112</v>
+        <v>1713502702</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5073,10 +5221,11 @@
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5244,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1710787894</v>
+        <v>1713508978</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5105,10 +5254,11 @@
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5277,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1710801222</v>
+        <v>1713518470</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5141,6 +5291,7 @@
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5310,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1710808208</v>
+        <v>1713521177</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5169,10 +5320,11 @@
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5343,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1710817074</v>
+        <v>1713521954</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5201,10 +5353,11 @@
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5376,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1710821857</v>
+        <v>1713555368</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5233,10 +5386,11 @@
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5409,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1710829781</v>
+        <v>1713572128</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5269,6 +5423,7 @@
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5287,7 +5442,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1710831640</v>
+        <v>1713580862</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5297,10 +5452,11 @@
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5319,7 +5475,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1710832340</v>
+        <v>1713592308</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5329,10 +5485,11 @@
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5351,7 +5508,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1710873023</v>
+        <v>1713597631</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5361,10 +5518,11 @@
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5383,7 +5541,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1710885051</v>
+        <v>1713607941</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5397,6 +5555,7 @@
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5415,7 +5574,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1710892204</v>
+        <v>1713610760</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5425,10 +5584,11 @@
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5447,7 +5607,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1710901273</v>
+        <v>1713611758</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5457,10 +5617,11 @@
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5479,7 +5640,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1710906055</v>
+        <v>1713640214</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5489,10 +5650,11 @@
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5511,7 +5673,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1710914745</v>
+        <v>1713656012</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5525,6 +5687,7 @@
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5543,7 +5706,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1710917224</v>
+        <v>1713664390</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5553,10 +5716,11 @@
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5575,7 +5739,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1710917887</v>
+        <v>1713673822</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5585,10 +5749,11 @@
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5607,7 +5772,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1710960649</v>
+        <v>1713679586</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5617,10 +5782,11 @@
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5639,7 +5805,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1710973425</v>
+        <v>1713689039</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5653,6 +5819,7 @@
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5671,7 +5838,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1710980160</v>
+        <v>1713690974</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5681,10 +5848,11 @@
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5703,7 +5871,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1710989477</v>
+        <v>1713691778</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5713,10 +5881,11 @@
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5735,7 +5904,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1710993890</v>
+        <v>1713726594</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5745,10 +5914,11 @@
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5767,7 +5937,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1711001292</v>
+        <v>1713742511</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5781,6 +5951,7 @@
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5799,7 +5970,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1711002929</v>
+        <v>1713751015</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5809,10 +5980,11 @@
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5831,7 +6003,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1711003742</v>
+        <v>1713760803</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5841,10 +6013,11 @@
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5863,7 +6036,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1711045699</v>
+        <v>1713767301</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5873,10 +6046,11 @@
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5895,7 +6069,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1711059589</v>
+        <v>1713776674</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5909,6 +6083,7 @@
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5927,7 +6102,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1711066888</v>
+        <v>1713778381</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5937,10 +6112,11 @@
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5959,7 +6135,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1711074664</v>
+        <v>1713779162</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5969,10 +6145,11 @@
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5991,7 +6168,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1711079450</v>
+        <v>1713812852</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6001,10 +6178,11 @@
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6023,7 +6201,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1711086870</v>
+        <v>1713829566</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6037,6 +6215,7 @@
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6055,7 +6234,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1711088631</v>
+        <v>1713837771</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6065,10 +6244,11 @@
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6087,7 +6267,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1711089193</v>
+        <v>1713848131</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6097,10 +6277,11 @@
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6119,7 +6300,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1711133202</v>
+        <v>1713854522</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -6129,10 +6310,11 @@
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6151,7 +6333,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1711146765</v>
+        <v>1713863605</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6165,6 +6347,7 @@
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6183,7 +6366,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1711153269</v>
+        <v>1713866001</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6193,10 +6376,11 @@
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6215,7 +6399,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1711161967</v>
+        <v>1713866855</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6225,10 +6409,11 @@
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6247,7 +6432,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1711166681</v>
+        <v>1713911224</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6257,10 +6442,11 @@
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6279,7 +6465,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1711173789</v>
+        <v>1713922629</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -6293,6 +6479,7 @@
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6311,7 +6498,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1711175466</v>
+        <v>1713931414</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -6321,10 +6508,11 @@
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
+          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6343,7 +6531,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1711176097</v>
+        <v>1713943023</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -6353,10 +6541,11 @@
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6375,7 +6564,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1711220733</v>
+        <v>1713950547</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -6389,6 +6578,7 @@
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6407,7 +6597,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1711235123</v>
+        <v>1713951991</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -6417,10 +6607,11 @@
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
+          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6439,7 +6630,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1711242357</v>
+        <v>1713998808</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6449,10 +6640,11 @@
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
+          <t>Context.UltravioletLevel.state: RelativelyLow</t>
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6471,7 +6663,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1711251045</v>
+        <v>1714009487</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6481,10 +6673,11 @@
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
+          <t>Context.UltravioletLevel.state: Moderate</t>
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6503,7 +6696,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1711256770</v>
+        <v>1714018054</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6517,6 +6710,7 @@
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6535,7 +6729,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1711265263</v>
+        <v>1714028946</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6549,6 +6743,7 @@
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6567,7 +6762,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1711267692</v>
+        <v>1714036168</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6581,6 +6776,7 @@
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6599,7 +6795,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1711268406</v>
+        <v>1714037521</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6613,6 +6809,7 @@
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6631,7 +6828,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1711306483</v>
+        <v>1714072179</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6645,6 +6842,7 @@
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6663,7 +6861,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1711320299</v>
+        <v>1714089038</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6677,6 +6875,7 @@
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6695,7 +6894,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1711327459</v>
+        <v>1714098052</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6709,6 +6908,7 @@
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6727,7 +6927,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1711336142</v>
+        <v>1714108916</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6741,6 +6941,7 @@
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6759,7 +6960,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1711341851</v>
+        <v>1714115405</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6773,6 +6974,7 @@
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6791,7 +6993,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1711350437</v>
+        <v>1714125415</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6805,6 +7007,7 @@
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6823,7 +7026,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1711352417</v>
+        <v>1714127535</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6837,6 +7040,7 @@
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6855,7 +7059,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1711353180</v>
+        <v>1714128493</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6869,6 +7073,7 @@
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6887,7 +7092,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1711393823</v>
+        <v>1714158659</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6901,6 +7106,7 @@
         </is>
       </c>
       <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6919,7 +7125,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1711410873</v>
+        <v>1714175184</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6933,6 +7139,7 @@
         </is>
       </c>
       <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6951,7 +7158,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1711419950</v>
+        <v>1714184062</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6965,6 +7172,7 @@
         </is>
       </c>
       <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6983,7 +7191,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1711431020</v>
+        <v>1714194898</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6997,6 +7205,7 @@
         </is>
       </c>
       <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7015,7 +7224,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1711437873</v>
+        <v>1714201397</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -7029,6 +7238,7 @@
         </is>
       </c>
       <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7047,7 +7257,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1711448421</v>
+        <v>1714211580</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -7061,6 +7271,7 @@
         </is>
       </c>
       <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7079,7 +7290,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1711451280</v>
+        <v>1714213962</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -7093,6 +7304,7 @@
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7111,7 +7323,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1711452111</v>
+        <v>1714214881</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7125,6 +7337,7 @@
         </is>
       </c>
       <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7143,7 +7356,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1711480434</v>
+        <v>1714246004</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -7157,6 +7370,7 @@
         </is>
       </c>
       <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7175,7 +7389,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1711497369</v>
+        <v>1714262736</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -7189,6 +7403,7 @@
         </is>
       </c>
       <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7207,7 +7422,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1711506981</v>
+        <v>1714271965</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -7221,6 +7436,7 @@
         </is>
       </c>
       <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7239,7 +7455,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1711518850</v>
+        <v>1714282414</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -7253,6 +7469,7 @@
         </is>
       </c>
       <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7271,7 +7488,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1711526170</v>
+        <v>1714287840</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -7285,6 +7502,7 @@
         </is>
       </c>
       <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7303,7 +7521,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1711536743</v>
+        <v>1714298175</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -7317,6 +7535,7 @@
         </is>
       </c>
       <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7335,7 +7554,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1711538939</v>
+        <v>1714300848</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -7349,6 +7568,7 @@
         </is>
       </c>
       <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7367,7 +7587,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1711539817</v>
+        <v>1714301968</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -7381,262 +7601,7 @@
         </is>
       </c>
       <c r="H217" t="inlineStr"/>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>1711567213</v>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr"/>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>1711583583</v>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr"/>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>1711592365</v>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr"/>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr"/>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>1711604041</v>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyHigh</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr"/>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>1711610600</v>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>Context.UltravioletLevel.state: RelativelyHigh</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr"/>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D223" t="n">
-        <v>1711621197</v>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr"/>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>Context.UltravioletLevel.state: Moderate</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr"/>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D224" t="n">
-        <v>1711623804</v>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>Context.UltravioletLevel.state: RelativelyLow</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr"/>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>UltravioletLevel_Change</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="D225" t="n">
-        <v>1711624689</v>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr"/>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>Context.UltravioletLevel.state: ExcessivelyLow</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
